--- a/pptx-server/키즈밀_식단표_기준폼_v6.xlsx
+++ b/pptx-server/키즈밀_식단표_기준폼_v6.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1주차" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="49">
+  <fonts count="59">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -389,6 +389,65 @@
       <family val="3"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <i val="1"/>
+      <color rgb="FF212121"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FF37474F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FFE65100"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FF1B5E20"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FFB71C1C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FFBF360C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FF5D3A00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <color rgb="FF880E4F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <i val="1"/>
+      <color rgb="FFB71C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <color rgb="FF424242"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -680,6 +739,30 @@
       <left/>
       <right/>
       <top style="thin">
+        <color rgb="FFB4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color rgb="FFBDBDBD"/>
       </top>
       <bottom/>
@@ -707,30 +790,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFB4C6E7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB4C6E7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB4C6E7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB4C6E7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FFBDBDBD"/>
       </right>
@@ -744,7 +803,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1005,10 +1064,12 @@
     <xf numFmtId="0" fontId="48" fillId="33" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="31" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1022,8 +1083,39 @@
     <xf numFmtId="0" fontId="35" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1285,13 +1377,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col width="9" customWidth="1" style="88" min="1" max="1"/>
-    <col width="28" customWidth="1" style="88" min="2" max="6"/>
+    <col width="9" customWidth="1" style="91" min="1" max="1"/>
+    <col width="28" customWidth="1" style="91" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="88">
+    <row r="1" ht="25.5" customHeight="1" s="91">
       <c r="A1" s="82" t="inlineStr">
         <is>
           <t>2026년 6월 식단표  [CK]  —  1주차</t>
@@ -1303,7 +1395,7 @@
       <c r="E1" s="81" t="n"/>
       <c r="F1" s="81" t="n"/>
     </row>
-    <row r="2" ht="36.75" customHeight="1" s="88">
+    <row r="2" ht="36.75" customHeight="1" s="91">
       <c r="A2" s="84" t="inlineStr">
         <is>
           <t>작성 영양사:                   작성일:</t>
@@ -1311,7 +1403,7 @@
       </c>
       <c r="B2" s="81" t="n"/>
       <c r="C2" s="81" t="n"/>
-      <c r="D2" s="80" t="inlineStr">
+      <c r="D2" s="97" t="inlineStr">
         <is>
           <t>※ 알러지: 원문자 직접입력(①②③...)  |  영양구성: 466Kcal(탄59단16지23) 형식 그대로  |  후식과일: 원별특이사항에 [후식과일]  |  공휴일 중식 입력 금지</t>
         </is>
@@ -1319,7 +1411,7 @@
       <c r="E2" s="81" t="n"/>
       <c r="F2" s="81" t="n"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="88">
+    <row r="3" ht="21.75" customHeight="1" s="91">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>구분</t>
@@ -1353,8 +1445,8 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="88">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="91">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>밥</t>
         </is>
@@ -1369,8 +1461,8 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1" s="88">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="91">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>국</t>
         </is>
@@ -1385,8 +1477,8 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1" s="88">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="24" customHeight="1" s="91">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>반찬1</t>
         </is>
@@ -1401,8 +1493,8 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1" s="88">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="24" customHeight="1" s="91">
+      <c r="A7" s="98" t="inlineStr">
         <is>
           <t>반찬2</t>
         </is>
@@ -1417,8 +1509,8 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1" s="88">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="24" customHeight="1" s="91">
+      <c r="A8" s="98" t="inlineStr">
         <is>
           <t>반찬3</t>
         </is>
@@ -1433,8 +1525,8 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1" s="88">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="24" customHeight="1" s="91">
+      <c r="A9" s="98" t="inlineStr">
         <is>
           <t>반찬4</t>
         </is>
@@ -1449,24 +1541,24 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1" s="88">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="24" customHeight="1" s="91">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>반찬5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="100" t="n"/>
       <c r="D10" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="88">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="E10" s="100" t="n"/>
+      <c r="F10" s="100" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="91">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -1481,8 +1573,8 @@
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="88">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="12" s="91">
+      <c r="A12" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -1493,8 +1585,8 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="12" t="n"/>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="88">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="21.75" customHeight="1" s="91">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -1505,8 +1597,8 @@
       <c r="E13" s="14" t="n"/>
       <c r="F13" s="14" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="88">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="91">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>오전간식</t>
         </is>
@@ -1517,8 +1609,8 @@
       <c r="E14" s="16" t="n"/>
       <c r="F14" s="16" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="88">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="91">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -1533,8 +1625,8 @@
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="88">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="16" s="91">
+      <c r="A16" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -1545,8 +1637,8 @@
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="12" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="88">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="18" customHeight="1" s="91">
+      <c r="A17" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -1557,8 +1649,8 @@
       <c r="E17" s="14" t="n"/>
       <c r="F17" s="14" t="n"/>
     </row>
-    <row r="18" ht="21.75" customHeight="1" s="88">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="18" ht="21.75" customHeight="1" s="91">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>생일간식</t>
         </is>
@@ -1585,8 +1677,8 @@
       </c>
       <c r="F18" s="19" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1" s="88">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="91">
+      <c r="A19" s="104" t="inlineStr">
         <is>
           <t>오후간식</t>
         </is>
@@ -1597,8 +1689,8 @@
       <c r="E19" s="16" t="n"/>
       <c r="F19" s="16" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="88">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="20" ht="18" customHeight="1" s="91">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -1613,8 +1705,8 @@
       <c r="E20" s="10" t="n"/>
       <c r="F20" s="10" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="88">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="21" s="91">
+      <c r="A21" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -1625,8 +1717,8 @@
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="12" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="88">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="22" ht="18" customHeight="1" s="91">
+      <c r="A22" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -1637,8 +1729,8 @@
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="14" t="n"/>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="88">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="23" ht="21.75" customHeight="1" s="91">
+      <c r="A23" s="106" t="inlineStr">
         <is>
           <t>돌봄간식</t>
         </is>
@@ -1653,8 +1745,8 @@
       <c r="E23" s="21" t="n"/>
       <c r="F23" s="21" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="88">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="24" ht="18" customHeight="1" s="91">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -1669,10 +1761,10 @@
       <c r="E24" s="10" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
-    <row r="25" ht="19.5" customHeight="1" s="88">
-      <c r="A25" s="83" t="inlineStr">
-        <is>
-          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일  ■ 반찬5=없으면 빈칸</t>
+    <row r="25" ht="19.5" customHeight="1" s="91">
+      <c r="A25" s="107" t="inlineStr">
+        <is>
+          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일</t>
         </is>
       </c>
       <c r="B25" s="81" t="n"/>
@@ -1681,8 +1773,8 @@
       <c r="E25" s="81" t="n"/>
       <c r="F25" s="81" t="n"/>
     </row>
-    <row r="26" ht="19.5" customHeight="1" s="88">
-      <c r="A26" s="83" t="inlineStr">
+    <row r="26" ht="19.5" customHeight="1" s="91">
+      <c r="A26" s="107" t="inlineStr">
         <is>
           <t>■ 반찬3·4·5 없으면 빈칸  ■ 국 없는 날(볶음밥 등) 빈칸  ■ 후식과일: 원별특이사항에 [후식과일] (잉파·엘란만)  ■ 돌봄간식: 송파ECC만  ■ 5주차 없는 달: 날짜행 '해당없음'</t>
         </is>
@@ -1702,7 +1794,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.279861111111111" right="0.279861111111111" top="0.4" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1714,13 +1806,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col width="9" customWidth="1" style="88" min="1" max="1"/>
-    <col width="28" customWidth="1" style="88" min="2" max="6"/>
+    <col width="9" customWidth="1" style="91" min="1" max="1"/>
+    <col width="28" customWidth="1" style="91" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="88">
+    <row r="1" ht="25.5" customHeight="1" s="91">
       <c r="A1" s="82" t="inlineStr">
         <is>
           <t>2026년 6월 식단표  [CK]  —  2주차</t>
@@ -1732,7 +1824,7 @@
       <c r="E1" s="81" t="n"/>
       <c r="F1" s="81" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="88">
+    <row r="2" ht="36.75" customHeight="1" s="91">
       <c r="A2" s="84" t="inlineStr">
         <is>
           <t>작성 영양사:                   작성일:</t>
@@ -1740,7 +1832,7 @@
       </c>
       <c r="B2" s="81" t="n"/>
       <c r="C2" s="81" t="n"/>
-      <c r="D2" s="80" t="inlineStr">
+      <c r="D2" s="97" t="inlineStr">
         <is>
           <t>※ 알러지: 원문자 직접입력(①②③...)  |  영양구성: 466Kcal(탄59단16지23) 형식 그대로  |  후식과일: 원별특이사항에 [후식과일]  |  공휴일 중식 입력 금지</t>
         </is>
@@ -1748,7 +1840,7 @@
       <c r="E2" s="81" t="n"/>
       <c r="F2" s="81" t="n"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="88">
+    <row r="3" ht="21.75" customHeight="1" s="91">
       <c r="A3" s="23" t="inlineStr">
         <is>
           <t>구분</t>
@@ -1780,8 +1872,8 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="88">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="91">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>밥</t>
         </is>
@@ -1792,8 +1884,8 @@
       <c r="E4" s="24" t="n"/>
       <c r="F4" s="24" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1" s="88">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="91">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>국</t>
         </is>
@@ -1804,8 +1896,8 @@
       <c r="E5" s="24" t="n"/>
       <c r="F5" s="24" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1" s="88">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="24" customHeight="1" s="91">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>반찬1</t>
         </is>
@@ -1816,8 +1908,8 @@
       <c r="E6" s="24" t="n"/>
       <c r="F6" s="24" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1" s="88">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="24" customHeight="1" s="91">
+      <c r="A7" s="98" t="inlineStr">
         <is>
           <t>반찬2</t>
         </is>
@@ -1828,8 +1920,8 @@
       <c r="E7" s="24" t="n"/>
       <c r="F7" s="24" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1" s="88">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="24" customHeight="1" s="91">
+      <c r="A8" s="98" t="inlineStr">
         <is>
           <t>반찬3</t>
         </is>
@@ -1840,8 +1932,8 @@
       <c r="E8" s="24" t="n"/>
       <c r="F8" s="24" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1" s="88">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="24" customHeight="1" s="91">
+      <c r="A9" s="98" t="inlineStr">
         <is>
           <t>반찬4</t>
         </is>
@@ -1852,20 +1944,20 @@
       <c r="E9" s="24" t="n"/>
       <c r="F9" s="24" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1" s="88">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="24" customHeight="1" s="91">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>반찬5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="88">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="100" t="n"/>
+      <c r="D10" s="100" t="n"/>
+      <c r="E10" s="100" t="n"/>
+      <c r="F10" s="100" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="91">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -1876,8 +1968,8 @@
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="88">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="12" s="91">
+      <c r="A12" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -1888,8 +1980,8 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="12" t="n"/>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="88">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="21.75" customHeight="1" s="91">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -1900,8 +1992,8 @@
       <c r="E13" s="14" t="n"/>
       <c r="F13" s="14" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="88">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="91">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>오전간식</t>
         </is>
@@ -1912,8 +2004,8 @@
       <c r="E14" s="16" t="n"/>
       <c r="F14" s="16" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="88">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="91">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -1924,8 +2016,8 @@
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="88">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="16" s="91">
+      <c r="A16" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -1936,8 +2028,8 @@
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="12" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="88">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="18" customHeight="1" s="91">
+      <c r="A17" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -1948,8 +2040,8 @@
       <c r="E17" s="14" t="n"/>
       <c r="F17" s="14" t="n"/>
     </row>
-    <row r="18" ht="21.75" customHeight="1" s="88">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="18" ht="21.75" customHeight="1" s="91">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>생일간식</t>
         </is>
@@ -1976,8 +2068,8 @@
       </c>
       <c r="F18" s="19" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1" s="88">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="91">
+      <c r="A19" s="104" t="inlineStr">
         <is>
           <t>오후간식</t>
         </is>
@@ -1988,8 +2080,8 @@
       <c r="E19" s="16" t="n"/>
       <c r="F19" s="16" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="88">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="20" ht="18" customHeight="1" s="91">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2000,8 +2092,8 @@
       <c r="E20" s="10" t="n"/>
       <c r="F20" s="10" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="88">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="21" s="91">
+      <c r="A21" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -2012,8 +2104,8 @@
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="12" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="88">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="22" ht="18" customHeight="1" s="91">
+      <c r="A22" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -2024,8 +2116,8 @@
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="14" t="n"/>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="88">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="23" ht="21.75" customHeight="1" s="91">
+      <c r="A23" s="106" t="inlineStr">
         <is>
           <t>돌봄간식</t>
         </is>
@@ -2036,8 +2128,8 @@
       <c r="E23" s="21" t="n"/>
       <c r="F23" s="21" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="88">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="24" ht="18" customHeight="1" s="91">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2048,10 +2140,10 @@
       <c r="E24" s="10" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
-    <row r="25" ht="19.5" customHeight="1" s="88">
-      <c r="A25" s="83" t="inlineStr">
-        <is>
-          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일  ■ 반찬5=없으면 빈칸</t>
+    <row r="25" ht="19.5" customHeight="1" s="91">
+      <c r="A25" s="107" t="inlineStr">
+        <is>
+          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일</t>
         </is>
       </c>
       <c r="B25" s="81" t="n"/>
@@ -2060,8 +2152,8 @@
       <c r="E25" s="81" t="n"/>
       <c r="F25" s="81" t="n"/>
     </row>
-    <row r="26" ht="19.5" customHeight="1" s="88">
-      <c r="A26" s="83" t="inlineStr">
+    <row r="26" ht="19.5" customHeight="1" s="91">
+      <c r="A26" s="107" t="inlineStr">
         <is>
           <t>■ 반찬3·4·5 없으면 빈칸  ■ 국 없는 날(볶음밥 등) 빈칸  ■ 후식과일: 원별특이사항에 [후식과일] (잉파·엘란만)  ■ 돌봄간식: 송파ECC만  ■ 5주차 없는 달: 날짜행 '해당없음'</t>
         </is>
@@ -2081,7 +2173,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.279861111111111" right="0.279861111111111" top="0.4" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -2093,13 +2185,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col width="9" customWidth="1" style="88" min="1" max="1"/>
-    <col width="28" customWidth="1" style="88" min="2" max="6"/>
+    <col width="9" customWidth="1" style="91" min="1" max="1"/>
+    <col width="28" customWidth="1" style="91" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="88">
+    <row r="1" ht="25.5" customHeight="1" s="91">
       <c r="A1" s="82" t="inlineStr">
         <is>
           <t>2026년 6월 식단표  [CK]  —  3주차</t>
@@ -2111,7 +2203,7 @@
       <c r="E1" s="81" t="n"/>
       <c r="F1" s="81" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="88">
+    <row r="2" ht="36.75" customHeight="1" s="91">
       <c r="A2" s="84" t="inlineStr">
         <is>
           <t>작성 영양사:                   작성일:</t>
@@ -2119,7 +2211,7 @@
       </c>
       <c r="B2" s="81" t="n"/>
       <c r="C2" s="81" t="n"/>
-      <c r="D2" s="80" t="inlineStr">
+      <c r="D2" s="97" t="inlineStr">
         <is>
           <t>※ 알러지: 원문자 직접입력(①②③...)  |  영양구성: 466Kcal(탄59단16지23) 형식 그대로  |  후식과일: 원별특이사항에 [후식과일]  |  공휴일 중식 입력 금지</t>
         </is>
@@ -2127,7 +2219,7 @@
       <c r="E2" s="81" t="n"/>
       <c r="F2" s="81" t="n"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="88">
+    <row r="3" ht="21.75" customHeight="1" s="91">
       <c r="A3" s="25" t="inlineStr">
         <is>
           <t>구분</t>
@@ -2159,8 +2251,8 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="88">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="91">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>밥</t>
         </is>
@@ -2171,8 +2263,8 @@
       <c r="E4" s="26" t="n"/>
       <c r="F4" s="26" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1" s="88">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="91">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>국</t>
         </is>
@@ -2183,8 +2275,8 @@
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1" s="88">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="24" customHeight="1" s="91">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>반찬1</t>
         </is>
@@ -2195,8 +2287,8 @@
       <c r="E6" s="26" t="n"/>
       <c r="F6" s="26" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1" s="88">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="24" customHeight="1" s="91">
+      <c r="A7" s="98" t="inlineStr">
         <is>
           <t>반찬2</t>
         </is>
@@ -2207,8 +2299,8 @@
       <c r="E7" s="26" t="n"/>
       <c r="F7" s="26" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1" s="88">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="24" customHeight="1" s="91">
+      <c r="A8" s="98" t="inlineStr">
         <is>
           <t>반찬3</t>
         </is>
@@ -2219,8 +2311,8 @@
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="26" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1" s="88">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="24" customHeight="1" s="91">
+      <c r="A9" s="98" t="inlineStr">
         <is>
           <t>반찬4</t>
         </is>
@@ -2231,20 +2323,20 @@
       <c r="E9" s="26" t="n"/>
       <c r="F9" s="26" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1" s="88">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="24" customHeight="1" s="91">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>반찬5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="88">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="100" t="n"/>
+      <c r="D10" s="100" t="n"/>
+      <c r="E10" s="100" t="n"/>
+      <c r="F10" s="100" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="91">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2255,8 +2347,8 @@
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="88">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="12" s="91">
+      <c r="A12" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -2267,8 +2359,8 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="12" t="n"/>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="88">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="21.75" customHeight="1" s="91">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -2279,8 +2371,8 @@
       <c r="E13" s="14" t="n"/>
       <c r="F13" s="14" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="88">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="91">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>오전간식</t>
         </is>
@@ -2291,8 +2383,8 @@
       <c r="E14" s="16" t="n"/>
       <c r="F14" s="16" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="88">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="91">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2303,8 +2395,8 @@
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="88">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="16" s="91">
+      <c r="A16" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -2315,8 +2407,8 @@
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="12" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="88">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="18" customHeight="1" s="91">
+      <c r="A17" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -2327,8 +2419,8 @@
       <c r="E17" s="14" t="n"/>
       <c r="F17" s="14" t="n"/>
     </row>
-    <row r="18" ht="21.75" customHeight="1" s="88">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="18" ht="21.75" customHeight="1" s="91">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>생일간식</t>
         </is>
@@ -2355,8 +2447,8 @@
       </c>
       <c r="F18" s="19" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1" s="88">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="91">
+      <c r="A19" s="104" t="inlineStr">
         <is>
           <t>오후간식</t>
         </is>
@@ -2367,8 +2459,8 @@
       <c r="E19" s="16" t="n"/>
       <c r="F19" s="16" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="88">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="20" ht="18" customHeight="1" s="91">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2379,8 +2471,8 @@
       <c r="E20" s="10" t="n"/>
       <c r="F20" s="10" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="88">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="21" s="91">
+      <c r="A21" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -2391,8 +2483,8 @@
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="12" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="88">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="22" ht="18" customHeight="1" s="91">
+      <c r="A22" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -2403,8 +2495,8 @@
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="14" t="n"/>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="88">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="23" ht="21.75" customHeight="1" s="91">
+      <c r="A23" s="106" t="inlineStr">
         <is>
           <t>돌봄간식</t>
         </is>
@@ -2415,8 +2507,8 @@
       <c r="E23" s="21" t="n"/>
       <c r="F23" s="21" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="88">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="24" ht="18" customHeight="1" s="91">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2427,10 +2519,10 @@
       <c r="E24" s="10" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
-    <row r="25" ht="19.5" customHeight="1" s="88">
-      <c r="A25" s="83" t="inlineStr">
-        <is>
-          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일  ■ 반찬5=없으면 빈칸</t>
+    <row r="25" ht="19.5" customHeight="1" s="91">
+      <c r="A25" s="107" t="inlineStr">
+        <is>
+          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일</t>
         </is>
       </c>
       <c r="B25" s="81" t="n"/>
@@ -2439,8 +2531,8 @@
       <c r="E25" s="81" t="n"/>
       <c r="F25" s="81" t="n"/>
     </row>
-    <row r="26" ht="19.5" customHeight="1" s="88">
-      <c r="A26" s="83" t="inlineStr">
+    <row r="26" ht="19.5" customHeight="1" s="91">
+      <c r="A26" s="107" t="inlineStr">
         <is>
           <t>■ 반찬3·4·5 없으면 빈칸  ■ 국 없는 날(볶음밥 등) 빈칸  ■ 후식과일: 원별특이사항에 [후식과일] (잉파·엘란만)  ■ 돌봄간식: 송파ECC만  ■ 5주차 없는 달: 날짜행 '해당없음'</t>
         </is>
@@ -2460,7 +2552,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.279861111111111" right="0.279861111111111" top="0.4" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -2472,13 +2564,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col width="9" customWidth="1" style="88" min="1" max="1"/>
-    <col width="28" customWidth="1" style="88" min="2" max="6"/>
+    <col width="9" customWidth="1" style="91" min="1" max="1"/>
+    <col width="28" customWidth="1" style="91" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="88">
+    <row r="1" ht="25.5" customHeight="1" s="91">
       <c r="A1" s="82" t="inlineStr">
         <is>
           <t>2026년 6월 식단표  [CK]  —  4주차</t>
@@ -2490,7 +2582,7 @@
       <c r="E1" s="81" t="n"/>
       <c r="F1" s="81" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="88">
+    <row r="2" ht="36.75" customHeight="1" s="91">
       <c r="A2" s="84" t="inlineStr">
         <is>
           <t>작성 영양사:                   작성일:</t>
@@ -2498,7 +2590,7 @@
       </c>
       <c r="B2" s="81" t="n"/>
       <c r="C2" s="81" t="n"/>
-      <c r="D2" s="80" t="inlineStr">
+      <c r="D2" s="97" t="inlineStr">
         <is>
           <t>※ 알러지: 원문자 직접입력(①②③...)  |  영양구성: 466Kcal(탄59단16지23) 형식 그대로  |  후식과일: 원별특이사항에 [후식과일]  |  공휴일 중식 입력 금지</t>
         </is>
@@ -2506,7 +2598,7 @@
       <c r="E2" s="81" t="n"/>
       <c r="F2" s="81" t="n"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="88">
+    <row r="3" ht="21.75" customHeight="1" s="91">
       <c r="A3" s="27" t="inlineStr">
         <is>
           <t>구분</t>
@@ -2538,8 +2630,8 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="88">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="91">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>밥</t>
         </is>
@@ -2550,8 +2642,8 @@
       <c r="E4" s="28" t="n"/>
       <c r="F4" s="28" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1" s="88">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="91">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>국</t>
         </is>
@@ -2562,8 +2654,8 @@
       <c r="E5" s="28" t="n"/>
       <c r="F5" s="28" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1" s="88">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="24" customHeight="1" s="91">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>반찬1</t>
         </is>
@@ -2574,8 +2666,8 @@
       <c r="E6" s="28" t="n"/>
       <c r="F6" s="28" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1" s="88">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="24" customHeight="1" s="91">
+      <c r="A7" s="98" t="inlineStr">
         <is>
           <t>반찬2</t>
         </is>
@@ -2586,8 +2678,8 @@
       <c r="E7" s="28" t="n"/>
       <c r="F7" s="28" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1" s="88">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="24" customHeight="1" s="91">
+      <c r="A8" s="98" t="inlineStr">
         <is>
           <t>반찬3</t>
         </is>
@@ -2598,8 +2690,8 @@
       <c r="E8" s="28" t="n"/>
       <c r="F8" s="28" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1" s="88">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="24" customHeight="1" s="91">
+      <c r="A9" s="98" t="inlineStr">
         <is>
           <t>반찬4</t>
         </is>
@@ -2610,20 +2702,20 @@
       <c r="E9" s="28" t="n"/>
       <c r="F9" s="28" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1" s="88">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="24" customHeight="1" s="91">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>반찬5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="88">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="100" t="n"/>
+      <c r="D10" s="100" t="n"/>
+      <c r="E10" s="100" t="n"/>
+      <c r="F10" s="100" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="91">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2634,8 +2726,8 @@
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="88">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="12" s="91">
+      <c r="A12" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -2646,8 +2738,8 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="12" t="n"/>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="88">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="21.75" customHeight="1" s="91">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -2658,8 +2750,8 @@
       <c r="E13" s="14" t="n"/>
       <c r="F13" s="14" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="88">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="91">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>오전간식</t>
         </is>
@@ -2670,8 +2762,8 @@
       <c r="E14" s="16" t="n"/>
       <c r="F14" s="16" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="88">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="91">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2682,8 +2774,8 @@
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="88">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="16" s="91">
+      <c r="A16" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -2694,8 +2786,8 @@
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="12" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="88">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="18" customHeight="1" s="91">
+      <c r="A17" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -2706,8 +2798,8 @@
       <c r="E17" s="14" t="n"/>
       <c r="F17" s="14" t="n"/>
     </row>
-    <row r="18" ht="21.75" customHeight="1" s="88">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="18" ht="21.75" customHeight="1" s="91">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>생일간식</t>
         </is>
@@ -2738,8 +2830,8 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="88">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="91">
+      <c r="A19" s="104" t="inlineStr">
         <is>
           <t>오후간식</t>
         </is>
@@ -2750,8 +2842,8 @@
       <c r="E19" s="16" t="n"/>
       <c r="F19" s="16" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="88">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="20" ht="18" customHeight="1" s="91">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2762,8 +2854,8 @@
       <c r="E20" s="10" t="n"/>
       <c r="F20" s="10" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="88">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="21" s="91">
+      <c r="A21" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -2774,8 +2866,8 @@
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="12" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="88">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="22" ht="18" customHeight="1" s="91">
+      <c r="A22" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -2786,8 +2878,8 @@
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="14" t="n"/>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="88">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="23" ht="21.75" customHeight="1" s="91">
+      <c r="A23" s="106" t="inlineStr">
         <is>
           <t>돌봄간식</t>
         </is>
@@ -2798,8 +2890,8 @@
       <c r="E23" s="21" t="n"/>
       <c r="F23" s="21" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="88">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="24" ht="18" customHeight="1" s="91">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -2810,10 +2902,10 @@
       <c r="E24" s="10" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
-    <row r="25" ht="19.5" customHeight="1" s="88">
-      <c r="A25" s="83" t="inlineStr">
-        <is>
-          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일  ■ 반찬5=없으면 빈칸</t>
+    <row r="25" ht="19.5" customHeight="1" s="91">
+      <c r="A25" s="107" t="inlineStr">
+        <is>
+          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일</t>
         </is>
       </c>
       <c r="B25" s="81" t="n"/>
@@ -2822,8 +2914,8 @@
       <c r="E25" s="81" t="n"/>
       <c r="F25" s="81" t="n"/>
     </row>
-    <row r="26" ht="19.5" customHeight="1" s="88">
-      <c r="A26" s="83" t="inlineStr">
+    <row r="26" ht="19.5" customHeight="1" s="91">
+      <c r="A26" s="107" t="inlineStr">
         <is>
           <t>■ 반찬3·4·5 없으면 빈칸  ■ 국 없는 날(볶음밥 등) 빈칸  ■ 후식과일: 원별특이사항에 [후식과일] (잉파·엘란만)  ■ 돌봄간식: 송파ECC만  ■ 5주차 없는 달: 날짜행 '해당없음'</t>
         </is>
@@ -2843,7 +2935,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.279861111111111" right="0.279861111111111" top="0.4" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -2855,13 +2947,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col width="9" customWidth="1" style="88" min="1" max="1"/>
-    <col width="28" customWidth="1" style="88" min="2" max="6"/>
+    <col width="9" customWidth="1" style="91" min="1" max="1"/>
+    <col width="28" customWidth="1" style="91" min="2" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="88">
+    <row r="1" ht="25.5" customHeight="1" s="91">
       <c r="A1" s="82" t="inlineStr">
         <is>
           <t>2026년 6월 식단표  [CK]  —  5주차</t>
@@ -2873,7 +2965,7 @@
       <c r="E1" s="81" t="n"/>
       <c r="F1" s="81" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="88">
+    <row r="2" ht="36.75" customHeight="1" s="91">
       <c r="A2" s="84" t="inlineStr">
         <is>
           <t>작성 영양사:                   작성일:</t>
@@ -2881,7 +2973,7 @@
       </c>
       <c r="B2" s="81" t="n"/>
       <c r="C2" s="81" t="n"/>
-      <c r="D2" s="80" t="inlineStr">
+      <c r="D2" s="97" t="inlineStr">
         <is>
           <t>※ 알러지: 원문자 직접입력(①②③...)  |  영양구성: 466Kcal(탄59단16지23) 형식 그대로  |  후식과일: 원별특이사항에 [후식과일]  |  공휴일 중식 입력 금지</t>
         </is>
@@ -2889,7 +2981,7 @@
       <c r="E2" s="81" t="n"/>
       <c r="F2" s="81" t="n"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="88">
+    <row r="3" ht="21.75" customHeight="1" s="91">
       <c r="A3" s="29" t="inlineStr">
         <is>
           <t>구분</t>
@@ -2921,8 +3013,8 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="88">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="91">
+      <c r="A4" s="98" t="inlineStr">
         <is>
           <t>밥</t>
         </is>
@@ -2933,8 +3025,8 @@
       <c r="E4" s="32" t="n"/>
       <c r="F4" s="32" t="n"/>
     </row>
-    <row r="5" ht="24" customHeight="1" s="88">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="24" customHeight="1" s="91">
+      <c r="A5" s="98" t="inlineStr">
         <is>
           <t>국</t>
         </is>
@@ -2945,8 +3037,8 @@
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n"/>
     </row>
-    <row r="6" ht="24" customHeight="1" s="88">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="24" customHeight="1" s="91">
+      <c r="A6" s="98" t="inlineStr">
         <is>
           <t>반찬1</t>
         </is>
@@ -2957,8 +3049,8 @@
       <c r="E6" s="32" t="n"/>
       <c r="F6" s="32" t="n"/>
     </row>
-    <row r="7" ht="24" customHeight="1" s="88">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="24" customHeight="1" s="91">
+      <c r="A7" s="98" t="inlineStr">
         <is>
           <t>반찬2</t>
         </is>
@@ -2969,8 +3061,8 @@
       <c r="E7" s="32" t="n"/>
       <c r="F7" s="32" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1" s="88">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="24" customHeight="1" s="91">
+      <c r="A8" s="98" t="inlineStr">
         <is>
           <t>반찬3</t>
         </is>
@@ -2981,8 +3073,8 @@
       <c r="E8" s="32" t="n"/>
       <c r="F8" s="32" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1" s="88">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="24" customHeight="1" s="91">
+      <c r="A9" s="98" t="inlineStr">
         <is>
           <t>반찬4</t>
         </is>
@@ -2993,20 +3085,20 @@
       <c r="E9" s="32" t="n"/>
       <c r="F9" s="32" t="n"/>
     </row>
-    <row r="10" ht="24" customHeight="1" s="88">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="24" customHeight="1" s="91">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>반찬5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="100" t="n"/>
       <c r="D10" s="32" t="n"/>
       <c r="E10" s="32" t="n"/>
       <c r="F10" s="32" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="88">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="11" ht="18" customHeight="1" s="91">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -3017,8 +3109,8 @@
       <c r="E11" s="32" t="n"/>
       <c r="F11" s="32" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="88">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="12" s="91">
+      <c r="A12" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -3029,8 +3121,8 @@
       <c r="E12" s="32" t="n"/>
       <c r="F12" s="32" t="n"/>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="88">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="21.75" customHeight="1" s="91">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -3041,8 +3133,8 @@
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="33" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="88">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="91">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>오전간식</t>
         </is>
@@ -3053,8 +3145,8 @@
       <c r="E14" s="32" t="n"/>
       <c r="F14" s="32" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="88">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="91">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -3065,8 +3157,8 @@
       <c r="E15" s="32" t="n"/>
       <c r="F15" s="32" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="88">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="16" s="91">
+      <c r="A16" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -3077,8 +3169,8 @@
       <c r="E16" s="32" t="n"/>
       <c r="F16" s="32" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="88">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="18" customHeight="1" s="91">
+      <c r="A17" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -3089,8 +3181,8 @@
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="33" t="n"/>
     </row>
-    <row r="18" ht="21.75" customHeight="1" s="88">
-      <c r="A18" s="17" t="inlineStr">
+    <row r="18" ht="21.75" customHeight="1" s="91">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>생일간식</t>
         </is>
@@ -3109,8 +3201,8 @@
       <c r="E18" s="33" t="n"/>
       <c r="F18" s="33" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1" s="88">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="19" ht="30" customHeight="1" s="91">
+      <c r="A19" s="104" t="inlineStr">
         <is>
           <t>오후간식</t>
         </is>
@@ -3121,8 +3213,8 @@
       <c r="E19" s="32" t="n"/>
       <c r="F19" s="32" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="88">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="20" ht="18" customHeight="1" s="91">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -3133,8 +3225,8 @@
       <c r="E20" s="32" t="n"/>
       <c r="F20" s="32" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="88">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="21" s="91">
+      <c r="A21" s="102" t="inlineStr">
         <is>
           <t>원별특이사항</t>
         </is>
@@ -3145,8 +3237,8 @@
       <c r="E21" s="32" t="n"/>
       <c r="F21" s="32" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="88">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="22" ht="18" customHeight="1" s="91">
+      <c r="A22" s="103" t="inlineStr">
         <is>
           <t>예외규칙</t>
         </is>
@@ -3157,8 +3249,8 @@
       <c r="E22" s="33" t="n"/>
       <c r="F22" s="33" t="n"/>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="88">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="23" ht="21.75" customHeight="1" s="91">
+      <c r="A23" s="106" t="inlineStr">
         <is>
           <t>돌봄간식</t>
         </is>
@@ -3169,8 +3261,8 @@
       <c r="E23" s="32" t="n"/>
       <c r="F23" s="32" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="88">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="24" ht="18" customHeight="1" s="91">
+      <c r="A24" s="101" t="inlineStr">
         <is>
           <t>영양구성</t>
         </is>
@@ -3181,10 +3273,10 @@
       <c r="E24" s="32" t="n"/>
       <c r="F24" s="32" t="n"/>
     </row>
-    <row r="25" ht="19.5" customHeight="1" s="88">
-      <c r="A25" s="83" t="inlineStr">
-        <is>
-          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일  ■ 반찬5=없으면 빈칸</t>
+    <row r="25" ht="19.5" customHeight="1" s="91">
+      <c r="A25" s="107" t="inlineStr">
+        <is>
+          <t>■ 연초록=영양구성  ■ 연노랑=원별특이사항 [원명-대체메뉴]/[후식과일]  ■ 연빨강=예외규칙 [원명-메뉴명X]/공휴일운영원  ■ 주황=생일주 금요일</t>
         </is>
       </c>
       <c r="B25" s="81" t="n"/>
@@ -3193,8 +3285,8 @@
       <c r="E25" s="81" t="n"/>
       <c r="F25" s="81" t="n"/>
     </row>
-    <row r="26" ht="19.5" customHeight="1" s="88">
-      <c r="A26" s="83" t="inlineStr">
+    <row r="26" ht="19.5" customHeight="1" s="91">
+      <c r="A26" s="107" t="inlineStr">
         <is>
           <t>■ 반찬3·4·5 없으면 빈칸  ■ 국 없는 날(볶음밥 등) 빈칸  ■ 후식과일: 원별특이사항에 [후식과일] (잉파·엘란만)  ■ 돌봄간식: 송파ECC만  ■ 5주차 없는 달: 날짜행 '해당없음'</t>
         </is>
@@ -3214,7 +3306,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.279861111111111" right="0.279861111111111" top="0.4" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -3228,14 +3320,14 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="88" min="1" max="1"/>
-    <col width="14" customWidth="1" style="88" min="2" max="2"/>
-    <col width="10" customWidth="1" style="88" min="3" max="3"/>
-    <col width="55" customWidth="1" style="88" min="4" max="4"/>
-    <col width="18" customWidth="1" style="88" min="5" max="5"/>
+    <col width="12" customWidth="1" style="91" min="1" max="1"/>
+    <col width="14" customWidth="1" style="91" min="2" max="2"/>
+    <col width="10" customWidth="1" style="91" min="3" max="3"/>
+    <col width="55" customWidth="1" style="91" min="4" max="4"/>
+    <col width="18" customWidth="1" style="91" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="88">
+    <row r="1" ht="24" customHeight="1" s="91">
       <c r="A1" s="85" t="inlineStr">
         <is>
           <t>도시락 · 대체식 요청 목록  (공휴일 / 특별 운영일)</t>
@@ -3246,7 +3338,7 @@
       <c r="D1" s="81" t="n"/>
       <c r="E1" s="81" t="n"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" s="88">
+    <row r="2" ht="21.75" customHeight="1" s="91">
       <c r="A2" s="80" t="inlineStr">
         <is>
           <t>※ 공휴일에도 운영하는 원 또는 도시락 요청 원을 날짜별로 입력하세요. 해당 없는 달은 비워두세요.</t>
@@ -3257,7 +3349,7 @@
       <c r="D2" s="81" t="n"/>
       <c r="E2" s="81" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="88">
+    <row r="3" ht="18" customHeight="1" s="91">
       <c r="A3" s="34" t="inlineStr">
         <is>
           <t>날짜</t>
@@ -3284,70 +3376,70 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="88">
+    <row r="4" ht="18" customHeight="1" s="91">
       <c r="A4" s="35" t="n"/>
       <c r="B4" s="36" t="n"/>
       <c r="C4" s="37" t="n"/>
       <c r="D4" s="36" t="n"/>
       <c r="E4" s="36" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="88">
+    <row r="5" ht="18" customHeight="1" s="91">
       <c r="A5" s="38" t="n"/>
       <c r="B5" s="39" t="n"/>
       <c r="C5" s="40" t="n"/>
       <c r="D5" s="39" t="n"/>
       <c r="E5" s="39" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1" s="88">
+    <row r="6" ht="18" customHeight="1" s="91">
       <c r="A6" s="35" t="n"/>
       <c r="B6" s="36" t="n"/>
       <c r="C6" s="37" t="n"/>
       <c r="D6" s="36" t="n"/>
       <c r="E6" s="41" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="88">
+    <row r="7" ht="18" customHeight="1" s="91">
       <c r="A7" s="42" t="n"/>
       <c r="B7" s="42" t="n"/>
       <c r="C7" s="42" t="n"/>
       <c r="D7" s="42" t="n"/>
       <c r="E7" s="42" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="88">
+    <row r="8" ht="18" customHeight="1" s="91">
       <c r="A8" s="43" t="n"/>
       <c r="B8" s="43" t="n"/>
       <c r="C8" s="43" t="n"/>
       <c r="D8" s="43" t="n"/>
       <c r="E8" s="43" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="88">
+    <row r="9" ht="18" customHeight="1" s="91">
       <c r="A9" s="42" t="n"/>
       <c r="B9" s="42" t="n"/>
       <c r="C9" s="42" t="n"/>
       <c r="D9" s="42" t="n"/>
       <c r="E9" s="42" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="88">
+    <row r="10" ht="18" customHeight="1" s="91">
       <c r="A10" s="43" t="n"/>
       <c r="B10" s="43" t="n"/>
       <c r="C10" s="43" t="n"/>
       <c r="D10" s="43" t="n"/>
       <c r="E10" s="43" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="88">
+    <row r="11" ht="18" customHeight="1" s="91">
       <c r="A11" s="42" t="n"/>
       <c r="B11" s="42" t="n"/>
       <c r="C11" s="42" t="n"/>
       <c r="D11" s="42" t="n"/>
       <c r="E11" s="42" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="88">
+    <row r="12" ht="18" customHeight="1" s="91">
       <c r="A12" s="43" t="n"/>
       <c r="B12" s="43" t="n"/>
       <c r="C12" s="43" t="n"/>
       <c r="D12" s="43" t="n"/>
       <c r="E12" s="43" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="88">
+    <row r="13" ht="18" customHeight="1" s="91">
       <c r="A13" s="42" t="n"/>
       <c r="B13" s="42" t="n"/>
       <c r="C13" s="42" t="n"/>
@@ -3374,19 +3466,19 @@
   <dimension ref="A1:P66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" style="88" min="1" max="1"/>
-    <col width="14" customWidth="1" style="88" min="2" max="2"/>
-    <col width="13" customWidth="1" style="88" min="3" max="3"/>
-    <col width="11" customWidth="1" style="88" min="4" max="4"/>
-    <col width="5" customWidth="1" style="88" min="5" max="6"/>
-    <col width="8" customWidth="1" style="88" min="7" max="7"/>
-    <col width="5" customWidth="1" style="88" min="8" max="8"/>
-    <col width="38" customWidth="1" style="88" min="9" max="9"/>
-    <col width="30" customWidth="1" style="88" min="10" max="10"/>
-    <col width="8" customWidth="1" style="88" min="11" max="16"/>
+    <col width="5" customWidth="1" style="91" min="1" max="1"/>
+    <col width="14" customWidth="1" style="91" min="2" max="2"/>
+    <col width="13" customWidth="1" style="91" min="3" max="3"/>
+    <col width="11" customWidth="1" style="91" min="4" max="4"/>
+    <col width="5" customWidth="1" style="91" min="5" max="6"/>
+    <col width="8" customWidth="1" style="91" min="7" max="7"/>
+    <col width="5" customWidth="1" style="91" min="8" max="8"/>
+    <col width="38" customWidth="1" style="91" min="9" max="9"/>
+    <col width="30" customWidth="1" style="91" min="10" max="10"/>
+    <col width="8" customWidth="1" style="91" min="11" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="88">
+    <row r="1" ht="24" customHeight="1" s="91">
       <c r="A1" s="86" t="inlineStr">
         <is>
           <t>원별 특이사항 참조표  —  대괄호 입력 시 D열 '메인식단표원명' 기준으로 정확히 입력</t>
@@ -3402,7 +3494,7 @@
       <c r="I1" s="81" t="n"/>
       <c r="J1" s="81" t="n"/>
     </row>
-    <row r="2" ht="19.5" customHeight="1" s="88">
+    <row r="2" ht="19.5" customHeight="1" s="91">
       <c r="A2" s="80" t="inlineStr">
         <is>
           <t>※ 이 시트는 수정하지 마세요. 참조 전용입니다. 원명 코드 확인 및 대괄호 입력 시 기준 자료로 사용하세요.</t>
@@ -3418,7 +3510,7 @@
       <c r="I2" s="81" t="n"/>
       <c r="J2" s="81" t="n"/>
     </row>
-    <row r="3" ht="31.5" customHeight="1" s="88">
+    <row r="3" ht="31.5" customHeight="1" s="91">
       <c r="A3" s="44" t="inlineStr">
         <is>
           <t>NO</t>
@@ -3506,7 +3598,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="88">
+    <row r="4" ht="15.75" customHeight="1" s="91">
       <c r="A4" s="46" t="n">
         <v>1</v>
       </c>
@@ -3574,7 +3666,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="88">
+    <row r="5" ht="15.75" customHeight="1" s="91">
       <c r="A5" s="52" t="n">
         <v>2</v>
       </c>
@@ -3642,7 +3734,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="88">
+    <row r="6" ht="15.75" customHeight="1" s="91">
       <c r="A6" s="46" t="n">
         <v>3</v>
       </c>
@@ -3710,7 +3802,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="88">
+    <row r="7" ht="15.75" customHeight="1" s="91">
       <c r="A7" s="52" t="n">
         <v>4</v>
       </c>
@@ -3778,7 +3870,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="88">
+    <row r="8" ht="15.75" customHeight="1" s="91">
       <c r="A8" s="46" t="n">
         <v>5</v>
       </c>
@@ -3854,7 +3946,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="88">
+    <row r="9" ht="15.75" customHeight="1" s="91">
       <c r="A9" s="52" t="n">
         <v>6</v>
       </c>
@@ -3926,7 +4018,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="88">
+    <row r="10" ht="15.75" customHeight="1" s="91">
       <c r="A10" s="46" t="n">
         <v>7</v>
       </c>
@@ -4006,7 +4098,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="88">
+    <row r="11" ht="15.75" customHeight="1" s="91">
       <c r="A11" s="52" t="n">
         <v>8</v>
       </c>
@@ -4078,7 +4170,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="88">
+    <row r="12" ht="15.75" customHeight="1" s="91">
       <c r="A12" s="46" t="n">
         <v>9</v>
       </c>
@@ -4146,7 +4238,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="88">
+    <row r="13" ht="15.75" customHeight="1" s="91">
       <c r="A13" s="52" t="n">
         <v>10</v>
       </c>
@@ -4214,7 +4306,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="88">
+    <row r="14" ht="15.75" customHeight="1" s="91">
       <c r="A14" s="46" t="n">
         <v>11</v>
       </c>
@@ -4286,7 +4378,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="88">
+    <row r="15" ht="15.75" customHeight="1" s="91">
       <c r="A15" s="52" t="n">
         <v>12</v>
       </c>
@@ -4362,7 +4454,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="88">
+    <row r="16" ht="15.75" customHeight="1" s="91">
       <c r="A16" s="46" t="n">
         <v>13</v>
       </c>
@@ -4438,7 +4530,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="88">
+    <row r="17" ht="15.75" customHeight="1" s="91">
       <c r="A17" s="52" t="n">
         <v>14</v>
       </c>
@@ -4510,7 +4602,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="88">
+    <row r="18" ht="15.75" customHeight="1" s="91">
       <c r="A18" s="46" t="n">
         <v>15</v>
       </c>
@@ -4578,7 +4670,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="88">
+    <row r="19" ht="15.75" customHeight="1" s="91">
       <c r="A19" s="52" t="n">
         <v>16</v>
       </c>
@@ -4654,7 +4746,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="88">
+    <row r="20" ht="15.75" customHeight="1" s="91">
       <c r="A20" s="46" t="n">
         <v>17</v>
       </c>
@@ -4726,7 +4818,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="88">
+    <row r="21" ht="15.75" customHeight="1" s="91">
       <c r="A21" s="52" t="n">
         <v>18</v>
       </c>
@@ -4802,7 +4894,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="88">
+    <row r="22" ht="15.75" customHeight="1" s="91">
       <c r="A22" s="46" t="n">
         <v>19</v>
       </c>
@@ -4874,7 +4966,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="88">
+    <row r="23" ht="15.75" customHeight="1" s="91">
       <c r="A23" s="52" t="n">
         <v>20</v>
       </c>
@@ -4946,7 +5038,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="88">
+    <row r="24" ht="15.75" customHeight="1" s="91">
       <c r="A24" s="46" t="n">
         <v>21</v>
       </c>
@@ -5018,7 +5110,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="88">
+    <row r="25" ht="15.75" customHeight="1" s="91">
       <c r="A25" s="52" t="n">
         <v>22</v>
       </c>
@@ -5090,7 +5182,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="88">
+    <row r="26" ht="15.75" customHeight="1" s="91">
       <c r="A26" s="46" t="n">
         <v>23</v>
       </c>
@@ -5162,7 +5254,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="88">
+    <row r="27" ht="15.75" customHeight="1" s="91">
       <c r="A27" s="52" t="n">
         <v>24</v>
       </c>
@@ -5238,7 +5330,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="88">
+    <row r="28" ht="15.75" customHeight="1" s="91">
       <c r="A28" s="46" t="n">
         <v>25</v>
       </c>
@@ -5306,7 +5398,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="88">
+    <row r="29" ht="15.75" customHeight="1" s="91">
       <c r="A29" s="52" t="n">
         <v>26</v>
       </c>
@@ -5374,7 +5466,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="88">
+    <row r="30" ht="15.75" customHeight="1" s="91">
       <c r="A30" s="46" t="n">
         <v>27</v>
       </c>
@@ -5446,7 +5538,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="88">
+    <row r="31" ht="15.75" customHeight="1" s="91">
       <c r="A31" s="52" t="n">
         <v>28</v>
       </c>
@@ -5518,7 +5610,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="88">
+    <row r="32" ht="15.75" customHeight="1" s="91">
       <c r="A32" s="46" t="n">
         <v>29</v>
       </c>
@@ -5590,7 +5682,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="88">
+    <row r="33" ht="15.75" customHeight="1" s="91">
       <c r="A33" s="52" t="n">
         <v>30</v>
       </c>
@@ -5662,7 +5754,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="88">
+    <row r="34" ht="15.75" customHeight="1" s="91">
       <c r="A34" s="46" t="n">
         <v>31</v>
       </c>
@@ -5734,7 +5826,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="88">
+    <row r="35" ht="15.75" customHeight="1" s="91">
       <c r="A35" s="52" t="n">
         <v>32</v>
       </c>
@@ -5806,7 +5898,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="88">
+    <row r="36" ht="15.75" customHeight="1" s="91">
       <c r="A36" s="46" t="n">
         <v>33</v>
       </c>
@@ -5878,7 +5970,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="88">
+    <row r="37" ht="15.75" customHeight="1" s="91">
       <c r="A37" s="52" t="n">
         <v>34</v>
       </c>
@@ -5950,7 +6042,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="88">
+    <row r="38" ht="15.75" customHeight="1" s="91">
       <c r="A38" s="46" t="n">
         <v>35</v>
       </c>
@@ -6022,7 +6114,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="88">
+    <row r="39" ht="15.75" customHeight="1" s="91">
       <c r="A39" s="52" t="n">
         <v>36</v>
       </c>
@@ -6094,7 +6186,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="88">
+    <row r="40" ht="15.75" customHeight="1" s="91">
       <c r="A40" s="46" t="n">
         <v>37</v>
       </c>
@@ -6166,7 +6258,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="88">
+    <row r="41" ht="15.75" customHeight="1" s="91">
       <c r="A41" s="52" t="n">
         <v>38</v>
       </c>
@@ -6242,7 +6334,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="88">
+    <row r="42" ht="15.75" customHeight="1" s="91">
       <c r="A42" s="46" t="n">
         <v>39</v>
       </c>
@@ -6314,7 +6406,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="88">
+    <row r="43" ht="15.75" customHeight="1" s="91">
       <c r="A43" s="52" t="n">
         <v>40</v>
       </c>
@@ -6386,7 +6478,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1" s="88">
+    <row r="44" ht="15.75" customHeight="1" s="91">
       <c r="A44" s="46" t="n">
         <v>41</v>
       </c>
@@ -6462,7 +6554,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="88">
+    <row r="45" ht="15.75" customHeight="1" s="91">
       <c r="A45" s="52" t="n">
         <v>42</v>
       </c>
@@ -6534,7 +6626,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="88">
+    <row r="46" ht="15.75" customHeight="1" s="91">
       <c r="A46" s="46" t="n">
         <v>43</v>
       </c>
@@ -6606,7 +6698,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="88">
+    <row r="47" ht="15.75" customHeight="1" s="91">
       <c r="A47" s="52" t="n">
         <v>44</v>
       </c>
@@ -6678,7 +6770,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="88">
+    <row r="48" ht="15.75" customHeight="1" s="91">
       <c r="A48" s="46" t="n">
         <v>45</v>
       </c>
@@ -6754,7 +6846,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1" s="88">
+    <row r="49" ht="15.75" customHeight="1" s="91">
       <c r="A49" s="52" t="n">
         <v>46</v>
       </c>
@@ -6830,7 +6922,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1" s="88">
+    <row r="50" ht="15.75" customHeight="1" s="91">
       <c r="A50" s="46" t="n">
         <v>47</v>
       </c>
@@ -6898,7 +6990,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1" s="88">
+    <row r="51" ht="15.75" customHeight="1" s="91">
       <c r="A51" s="52" t="n">
         <v>48</v>
       </c>
@@ -6974,7 +7066,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1" s="88">
+    <row r="52" ht="15.75" customHeight="1" s="91">
       <c r="A52" s="46" t="n">
         <v>49</v>
       </c>
@@ -7046,46 +7138,46 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="27.95" customHeight="1" s="88">
-      <c r="B61" s="89" t="inlineStr">
+    <row r="61" ht="27.95" customHeight="1" s="91">
+      <c r="B61" s="90" t="inlineStr">
         <is>
           <t>📋 공통 설정  —  원산지·원재료 (변경 시에만 수정)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="20.1" customHeight="1" s="88">
-      <c r="B62" s="91" t="inlineStr">
+    <row r="62" ht="20.1" customHeight="1" s="91">
+      <c r="B62" s="93" t="inlineStr">
         <is>
           <t>※ 아래 내용은 모든 원(園)에 공통 적용됩니다. 원산지·원재료가 변경될 때만 수정하세요.</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="21.95" customHeight="1" s="88">
-      <c r="B63" s="90" t="inlineStr">
+    <row r="63" ht="21.95" customHeight="1" s="91">
+      <c r="B63" s="92" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C63" s="90" t="inlineStr">
+      <c r="C63" s="92" t="inlineStr">
         <is>
           <t>내용 (변경 시 직접 수정)</t>
         </is>
       </c>
-      <c r="D63" s="95" t="n"/>
-      <c r="E63" s="95" t="n"/>
-      <c r="F63" s="95" t="n"/>
-      <c r="G63" s="95" t="n"/>
-      <c r="H63" s="95" t="n"/>
-      <c r="I63" s="95" t="n"/>
-      <c r="J63" s="95" t="n"/>
-      <c r="K63" s="95" t="n"/>
-      <c r="L63" s="95" t="n"/>
-      <c r="M63" s="95" t="n"/>
-      <c r="N63" s="95" t="n"/>
-      <c r="O63" s="95" t="n"/>
-      <c r="P63" s="96" t="n"/>
-    </row>
-    <row r="64" ht="45" customHeight="1" s="88">
+      <c r="D63" s="88" t="n"/>
+      <c r="E63" s="88" t="n"/>
+      <c r="F63" s="88" t="n"/>
+      <c r="G63" s="88" t="n"/>
+      <c r="H63" s="88" t="n"/>
+      <c r="I63" s="88" t="n"/>
+      <c r="J63" s="88" t="n"/>
+      <c r="K63" s="88" t="n"/>
+      <c r="L63" s="88" t="n"/>
+      <c r="M63" s="88" t="n"/>
+      <c r="N63" s="88" t="n"/>
+      <c r="O63" s="88" t="n"/>
+      <c r="P63" s="89" t="n"/>
+    </row>
+    <row r="64" ht="45" customHeight="1" s="91">
       <c r="B64" s="79" t="inlineStr">
         <is>
           <t>원산지 본문</t>
@@ -7096,21 +7188,21 @@
           <t>쌀·현미·흑미·찹쌀(국내산 친환경), 소고기(국내산 육우), 돼지고기(국내산), 닭고기(국내산), 오리고기(국내산 무항생제), 순두부·두부·콩비지(콩: 국내산), 배추김치(배추: 국내산, 고춧가루: 국내산), 아귀·오징어·고등어·꽃게(국내산), 명태(러시아산), 다랑어(원양산), 가다랑어포(인도네시아산)</t>
         </is>
       </c>
-      <c r="D64" s="95" t="n"/>
-      <c r="E64" s="95" t="n"/>
-      <c r="F64" s="95" t="n"/>
-      <c r="G64" s="95" t="n"/>
-      <c r="H64" s="95" t="n"/>
-      <c r="I64" s="95" t="n"/>
-      <c r="J64" s="95" t="n"/>
-      <c r="K64" s="95" t="n"/>
-      <c r="L64" s="95" t="n"/>
-      <c r="M64" s="95" t="n"/>
-      <c r="N64" s="95" t="n"/>
-      <c r="O64" s="95" t="n"/>
-      <c r="P64" s="96" t="n"/>
-    </row>
-    <row r="65" ht="30" customHeight="1" s="88">
+      <c r="D64" s="88" t="n"/>
+      <c r="E64" s="88" t="n"/>
+      <c r="F64" s="88" t="n"/>
+      <c r="G64" s="88" t="n"/>
+      <c r="H64" s="88" t="n"/>
+      <c r="I64" s="88" t="n"/>
+      <c r="J64" s="88" t="n"/>
+      <c r="K64" s="88" t="n"/>
+      <c r="L64" s="88" t="n"/>
+      <c r="M64" s="88" t="n"/>
+      <c r="N64" s="88" t="n"/>
+      <c r="O64" s="88" t="n"/>
+      <c r="P64" s="89" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1" s="91">
       <c r="B65" s="79" t="inlineStr">
         <is>
           <t>원산지 면책</t>
@@ -7121,21 +7213,21 @@
           <t>* 상기 원산지는 식자재 수급 사정에 따라 부득이하게 변경될 수 있습니다.</t>
         </is>
       </c>
-      <c r="D65" s="95" t="n"/>
-      <c r="E65" s="95" t="n"/>
-      <c r="F65" s="95" t="n"/>
-      <c r="G65" s="95" t="n"/>
-      <c r="H65" s="95" t="n"/>
-      <c r="I65" s="95" t="n"/>
-      <c r="J65" s="95" t="n"/>
-      <c r="K65" s="95" t="n"/>
-      <c r="L65" s="95" t="n"/>
-      <c r="M65" s="95" t="n"/>
-      <c r="N65" s="95" t="n"/>
-      <c r="O65" s="95" t="n"/>
-      <c r="P65" s="96" t="n"/>
-    </row>
-    <row r="66" ht="30" customHeight="1" s="88">
+      <c r="D65" s="88" t="n"/>
+      <c r="E65" s="88" t="n"/>
+      <c r="F65" s="88" t="n"/>
+      <c r="G65" s="88" t="n"/>
+      <c r="H65" s="88" t="n"/>
+      <c r="I65" s="88" t="n"/>
+      <c r="J65" s="88" t="n"/>
+      <c r="K65" s="88" t="n"/>
+      <c r="L65" s="88" t="n"/>
+      <c r="M65" s="88" t="n"/>
+      <c r="N65" s="88" t="n"/>
+      <c r="O65" s="88" t="n"/>
+      <c r="P65" s="89" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1" s="91">
       <c r="B66" s="79" t="inlineStr">
         <is>
           <t>원재료 안내</t>
@@ -7146,19 +7238,19 @@
           <t>햄/소시지(무항생제, 국내산 5無 또는 7無), 달걀(국내산 동물복지 유정란 또는 무항생제란)</t>
         </is>
       </c>
-      <c r="D66" s="95" t="n"/>
-      <c r="E66" s="95" t="n"/>
-      <c r="F66" s="95" t="n"/>
-      <c r="G66" s="95" t="n"/>
-      <c r="H66" s="95" t="n"/>
-      <c r="I66" s="95" t="n"/>
-      <c r="J66" s="95" t="n"/>
-      <c r="K66" s="95" t="n"/>
-      <c r="L66" s="95" t="n"/>
-      <c r="M66" s="95" t="n"/>
-      <c r="N66" s="95" t="n"/>
-      <c r="O66" s="95" t="n"/>
-      <c r="P66" s="96" t="n"/>
+      <c r="D66" s="88" t="n"/>
+      <c r="E66" s="88" t="n"/>
+      <c r="F66" s="88" t="n"/>
+      <c r="G66" s="88" t="n"/>
+      <c r="H66" s="88" t="n"/>
+      <c r="I66" s="88" t="n"/>
+      <c r="J66" s="88" t="n"/>
+      <c r="K66" s="88" t="n"/>
+      <c r="L66" s="88" t="n"/>
+      <c r="M66" s="88" t="n"/>
+      <c r="N66" s="88" t="n"/>
+      <c r="O66" s="88" t="n"/>
+      <c r="P66" s="89" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7186,35 +7278,35 @@
   <dimension ref="A1:C116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="88" min="1" max="1"/>
-    <col width="55" customWidth="1" style="88" min="2" max="2"/>
-    <col width="28" customWidth="1" style="88" min="3" max="3"/>
+    <col width="24" customWidth="1" style="91" min="1" max="1"/>
+    <col width="55" customWidth="1" style="91" min="2" max="2"/>
+    <col width="28" customWidth="1" style="91" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="88">
-      <c r="A1" s="92" t="inlineStr">
+    <row r="1" ht="19.5" customHeight="1" s="91">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>입력 가이드  —  CK 대표 영양사 전용</t>
         </is>
       </c>
       <c r="B1" s="81" t="n"/>
-      <c r="C1" s="93" t="n"/>
-    </row>
-    <row r="2" ht="19.5" customHeight="1" s="88">
-      <c r="A2" s="94" t="inlineStr">
+      <c r="C1" s="95" t="n"/>
+    </row>
+    <row r="2" ht="19.5" customHeight="1" s="91">
+      <c r="A2" s="96" t="inlineStr">
         <is>
           <t>규칙 변경 시에만 업데이트  |  평소에는 수정 불필요</t>
         </is>
       </c>
       <c r="B2" s="81" t="n"/>
-      <c r="C2" s="93" t="n"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" s="88">
+      <c r="C2" s="95" t="n"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" s="91">
       <c r="A3" s="41" t="n"/>
       <c r="B3" s="41" t="n"/>
       <c r="C3" s="41" t="n"/>
     </row>
-    <row r="4" ht="27" customHeight="1" s="88">
+    <row r="4" ht="27" customHeight="1" s="91">
       <c r="A4" s="67" t="inlineStr">
         <is>
           <t>📌 반찬5 행 추가 이유 (권팀장 참고)</t>
@@ -7223,7 +7315,7 @@
       <c r="B4" s="67" t="n"/>
       <c r="C4" s="67" t="n"/>
     </row>
-    <row r="5" ht="33" customHeight="1" s="88">
+    <row r="5" ht="33" customHeight="1" s="91">
       <c r="A5" s="36" t="inlineStr">
         <is>
           <t>반찬5 추가 배경</t>
@@ -7240,7 +7332,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="27.75" customHeight="1" s="88">
+    <row r="6" ht="27.75" customHeight="1" s="91">
       <c r="A6" s="68" t="inlineStr">
         <is>
           <t>해당 사례</t>
@@ -7257,7 +7349,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19.5" customHeight="1" s="88">
+    <row r="7" ht="19.5" customHeight="1" s="91">
       <c r="A7" s="36" t="inlineStr">
         <is>
           <t>입력 방법</t>
@@ -7270,12 +7362,12 @@
       </c>
       <c r="C7" s="41" t="n"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="88">
+    <row r="8" ht="15.75" customHeight="1" s="91">
       <c r="A8" s="68" t="n"/>
       <c r="B8" s="68" t="n"/>
       <c r="C8" s="68" t="n"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="88">
+    <row r="9" ht="15.75" customHeight="1" s="91">
       <c r="A9" s="69" t="inlineStr">
         <is>
           <t>📌 행 입력 순서 및 형식</t>
@@ -7292,7 +7384,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="88">
+    <row r="10" ht="15.75" customHeight="1" s="91">
       <c r="A10" s="68" t="inlineStr">
         <is>
           <t>밥</t>
@@ -7309,7 +7401,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="88">
+    <row r="11" ht="15.75" customHeight="1" s="91">
       <c r="A11" s="36" t="inlineStr">
         <is>
           <t>국</t>
@@ -7326,7 +7418,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="88">
+    <row r="12" ht="15.75" customHeight="1" s="91">
       <c r="A12" s="68" t="inlineStr">
         <is>
           <t>반찬1</t>
@@ -7343,7 +7435,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="88">
+    <row r="13" ht="15.75" customHeight="1" s="91">
       <c r="A13" s="36" t="inlineStr">
         <is>
           <t>반찬2</t>
@@ -7356,7 +7448,7 @@
       </c>
       <c r="C13" s="41" t="n"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="88">
+    <row r="14" ht="15.75" customHeight="1" s="91">
       <c r="A14" s="68" t="inlineStr">
         <is>
           <t>반찬3</t>
@@ -7373,7 +7465,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="88">
+    <row r="15" ht="15.75" customHeight="1" s="91">
       <c r="A15" s="36" t="inlineStr">
         <is>
           <t>반찬4</t>
@@ -7390,7 +7482,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="88">
+    <row r="16" ht="15.75" customHeight="1" s="91">
       <c r="A16" s="68" t="inlineStr">
         <is>
           <t>반찬5</t>
@@ -7407,7 +7499,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="88">
+    <row r="17" ht="15.75" customHeight="1" s="91">
       <c r="A17" s="36" t="inlineStr">
         <is>
           <t>영양구성 (중식)</t>
@@ -7424,7 +7516,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="88">
+    <row r="18" ht="15.75" customHeight="1" s="91">
       <c r="A18" s="68" t="inlineStr">
         <is>
           <t>원별특이사항 (중식)</t>
@@ -7441,7 +7533,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="88">
+    <row r="19" ht="15.75" customHeight="1" s="91">
       <c r="A19" s="36" t="inlineStr">
         <is>
           <t>예외규칙 (중식)</t>
@@ -7458,12 +7550,12 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="88">
+    <row r="20" ht="15.75" customHeight="1" s="91">
       <c r="A20" s="70" t="n"/>
       <c r="B20" s="70" t="n"/>
       <c r="C20" s="70" t="n"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="88">
+    <row r="21" ht="15.75" customHeight="1" s="91">
       <c r="A21" s="36" t="inlineStr">
         <is>
           <t>오전간식</t>
@@ -7480,7 +7572,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="88">
+    <row r="22" ht="15.75" customHeight="1" s="91">
       <c r="A22" s="68" t="inlineStr">
         <is>
           <t>영양구성 (오전)</t>
@@ -7493,7 +7585,7 @@
       </c>
       <c r="C22" s="70" t="n"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="88">
+    <row r="23" ht="15.75" customHeight="1" s="91">
       <c r="A23" s="36" t="inlineStr">
         <is>
           <t>원별특이사항 (오전)</t>
@@ -7506,7 +7598,7 @@
       </c>
       <c r="C23" s="41" t="n"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="88">
+    <row r="24" ht="15.75" customHeight="1" s="91">
       <c r="A24" s="68" t="inlineStr">
         <is>
           <t>예외규칙 (오전)</t>
@@ -7523,12 +7615,12 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="88">
+    <row r="25" ht="15.75" customHeight="1" s="91">
       <c r="A25" s="41" t="n"/>
       <c r="B25" s="41" t="n"/>
       <c r="C25" s="41" t="n"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="88">
+    <row r="26" ht="15.75" customHeight="1" s="91">
       <c r="A26" s="68" t="inlineStr">
         <is>
           <t>생일간식</t>
@@ -7545,12 +7637,12 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="88">
+    <row r="27" ht="15.75" customHeight="1" s="91">
       <c r="A27" s="41" t="n"/>
       <c r="B27" s="41" t="n"/>
       <c r="C27" s="41" t="n"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="88">
+    <row r="28" ht="15.75" customHeight="1" s="91">
       <c r="A28" s="68" t="inlineStr">
         <is>
           <t>오후간식</t>
@@ -7563,7 +7655,7 @@
       </c>
       <c r="C28" s="70" t="n"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="88">
+    <row r="29" ht="15.75" customHeight="1" s="91">
       <c r="A29" s="36" t="inlineStr">
         <is>
           <t>영양구성 (오후)</t>
@@ -7576,7 +7668,7 @@
       </c>
       <c r="C29" s="41" t="n"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="88">
+    <row r="30" ht="15.75" customHeight="1" s="91">
       <c r="A30" s="68" t="inlineStr">
         <is>
           <t>원별특이사항 (오후)</t>
@@ -7589,7 +7681,7 @@
       </c>
       <c r="C30" s="70" t="n"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="88">
+    <row r="31" ht="15.75" customHeight="1" s="91">
       <c r="A31" s="36" t="inlineStr">
         <is>
           <t>예외규칙 (오후)</t>
@@ -7602,12 +7694,12 @@
       </c>
       <c r="C31" s="41" t="n"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="88">
+    <row r="32" ht="15.75" customHeight="1" s="91">
       <c r="A32" s="70" t="n"/>
       <c r="B32" s="70" t="n"/>
       <c r="C32" s="70" t="n"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="88">
+    <row r="33" ht="15.75" customHeight="1" s="91">
       <c r="A33" s="36" t="inlineStr">
         <is>
           <t>돌봄간식</t>
@@ -7624,7 +7716,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="88">
+    <row r="34" ht="15.75" customHeight="1" s="91">
       <c r="A34" s="68" t="inlineStr">
         <is>
           <t>영양구성 (돌봄)</t>
@@ -7637,12 +7729,12 @@
       </c>
       <c r="C34" s="70" t="n"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="88">
+    <row r="35" ht="15.75" customHeight="1" s="91">
       <c r="A35" s="41" t="n"/>
       <c r="B35" s="41" t="n"/>
       <c r="C35" s="41" t="n"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="88">
+    <row r="36" ht="15.75" customHeight="1" s="91">
       <c r="A36" s="69" t="inlineStr">
         <is>
           <t>📌 우리만의 약속 키워드</t>
@@ -7659,7 +7751,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="88">
+    <row r="37" ht="15.75" customHeight="1" s="91">
       <c r="A37" s="41" t="inlineStr">
         <is>
           <t>[후식과일]</t>
@@ -7676,7 +7768,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="88">
+    <row r="38" ht="15.75" customHeight="1" s="91">
       <c r="A38" s="70" t="inlineStr">
         <is>
           <t>&lt;생일간식&gt;</t>
@@ -7693,12 +7785,12 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="88">
+    <row r="39" ht="15.75" customHeight="1" s="91">
       <c r="A39" s="41" t="n"/>
       <c r="B39" s="41" t="n"/>
       <c r="C39" s="41" t="n"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="88">
+    <row r="40" ht="15.75" customHeight="1" s="91">
       <c r="A40" s="69" t="inlineStr">
         <is>
           <t>📌 대괄호 규칙</t>
@@ -7715,7 +7807,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="88">
+    <row r="41" ht="15.75" customHeight="1" s="91">
       <c r="A41" s="41" t="inlineStr">
         <is>
           <t>[원명-대체메뉴]</t>
@@ -7732,7 +7824,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="88">
+    <row r="42" ht="15.75" customHeight="1" s="91">
       <c r="A42" s="70" t="inlineStr">
         <is>
           <t>[원명-메뉴명X]</t>
@@ -7749,7 +7841,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="88">
+    <row r="43" ht="15.75" customHeight="1" s="91">
       <c r="A43" s="41" t="inlineStr">
         <is>
           <t>[P-대체메뉴]</t>
@@ -7766,7 +7858,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1" s="88">
+    <row r="44" ht="15.75" customHeight="1" s="91">
       <c r="A44" s="70" t="inlineStr">
         <is>
           <t>[E-대체메뉴]</t>
@@ -7783,7 +7875,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="88">
+    <row r="45" ht="15.75" customHeight="1" s="91">
       <c r="A45" s="41" t="inlineStr">
         <is>
           <t>[R-대체메뉴]</t>
@@ -7800,7 +7892,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="88">
+    <row r="46" ht="15.75" customHeight="1" s="91">
       <c r="A46" s="68" t="inlineStr">
         <is>
           <t>복수원 동시</t>
@@ -7817,7 +7909,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="88">
+    <row r="47" ht="15.75" customHeight="1" s="91">
       <c r="A47" s="36" t="inlineStr">
         <is>
           <t>공휴일 운영원</t>
@@ -7834,12 +7926,12 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="88">
+    <row r="48" ht="15.75" customHeight="1" s="91">
       <c r="A48" s="70" t="n"/>
       <c r="B48" s="70" t="n"/>
       <c r="C48" s="70" t="n"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1" s="88">
+    <row r="49" ht="15.75" customHeight="1" s="91">
       <c r="A49" s="69" t="inlineStr">
         <is>
           <t>📌 알러지 원문자 — 아래에서 복사해서 사용</t>
@@ -7848,7 +7940,7 @@
       <c r="B49" s="69" t="n"/>
       <c r="C49" s="69" t="n"/>
     </row>
-    <row r="50" ht="19.5" customHeight="1" s="88">
+    <row r="50" ht="19.5" customHeight="1" s="91">
       <c r="A50" s="71" t="inlineStr">
         <is>
           <t>①=1  ②=2  ③=3  ④=4  ⑤=5  ⑥=6  ⑦=7  ⑧=8  ⑨=9  ⑩=10</t>
@@ -7861,7 +7953,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="19.5" customHeight="1" s="88">
+    <row r="51" ht="19.5" customHeight="1" s="91">
       <c r="A51" s="71" t="inlineStr">
         <is>
           <t>⑪=11  ⑫=12  ⑬=13  ⑭=14  ⑮=15  ⑯=16  ⑰=17  ⑱=18  ⑲=19</t>
@@ -7874,12 +7966,12 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1" s="88">
+    <row r="52" ht="15.75" customHeight="1" s="91">
       <c r="A52" s="70" t="n"/>
       <c r="B52" s="70" t="n"/>
       <c r="C52" s="70" t="n"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="88">
+    <row r="53" ht="15.75" customHeight="1" s="91">
       <c r="A53" s="69" t="inlineStr">
         <is>
           <t>📌 알러지 19종 번호표</t>
@@ -7888,7 +7980,7 @@
       <c r="B53" s="69" t="n"/>
       <c r="C53" s="69" t="n"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" s="88">
+    <row r="54" ht="15.75" customHeight="1" s="91">
       <c r="A54" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  ① 1번 = 난류</t>
@@ -7901,7 +7993,7 @@
       </c>
       <c r="C54" s="70" t="n"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1" s="88">
+    <row r="55" ht="15.75" customHeight="1" s="91">
       <c r="A55" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  ③ 3번 = 메밀</t>
@@ -7914,7 +8006,7 @@
       </c>
       <c r="C55" s="41" t="n"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" s="88">
+    <row r="56" ht="15.75" customHeight="1" s="91">
       <c r="A56" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑤ 5번 = 대두</t>
@@ -7927,7 +8019,7 @@
       </c>
       <c r="C56" s="70" t="n"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1" s="88">
+    <row r="57" ht="15.75" customHeight="1" s="91">
       <c r="A57" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑦ 7번 = 고등어</t>
@@ -7940,7 +8032,7 @@
       </c>
       <c r="C57" s="41" t="n"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" s="88">
+    <row r="58" ht="15.75" customHeight="1" s="91">
       <c r="A58" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑨ 9번 = 새우</t>
@@ -7953,7 +8045,7 @@
       </c>
       <c r="C58" s="70" t="n"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1" s="88">
+    <row r="59" ht="15.75" customHeight="1" s="91">
       <c r="A59" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑪ 11번 = 복숭아</t>
@@ -7966,7 +8058,7 @@
       </c>
       <c r="C59" s="41" t="n"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1" s="88">
+    <row r="60" ht="15.75" customHeight="1" s="91">
       <c r="A60" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑬ 13번 = 아황산류</t>
@@ -7979,7 +8071,7 @@
       </c>
       <c r="C60" s="70" t="n"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="88">
+    <row r="61" ht="15.75" customHeight="1" s="91">
       <c r="A61" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑮ 15번 = 닭고기</t>
@@ -7992,7 +8084,7 @@
       </c>
       <c r="C61" s="41" t="n"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1" s="88">
+    <row r="62" ht="15.75" customHeight="1" s="91">
       <c r="A62" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑰ 17번 = 오징어</t>
@@ -8005,7 +8097,7 @@
       </c>
       <c r="C62" s="70" t="n"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1" s="88">
+    <row r="63" ht="15.75" customHeight="1" s="91">
       <c r="A63" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑲ 19번 = 잣</t>
@@ -8014,12 +8106,12 @@
       <c r="B63" s="41" t="n"/>
       <c r="C63" s="41" t="n"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1" s="88">
+    <row r="64" ht="15.75" customHeight="1" s="91">
       <c r="A64" s="70" t="n"/>
       <c r="B64" s="70" t="n"/>
       <c r="C64" s="70" t="n"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1" s="88">
+    <row r="65" ht="15.75" customHeight="1" s="91">
       <c r="A65" s="69" t="inlineStr">
         <is>
           <t>📌 공휴일 처리</t>
@@ -8028,7 +8120,7 @@
       <c r="B65" s="69" t="n"/>
       <c r="C65" s="69" t="n"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1" s="88">
+    <row r="66" ht="15.75" customHeight="1" s="91">
       <c r="A66" s="68" t="inlineStr">
         <is>
           <t>중식 입력 금지</t>
@@ -8045,7 +8137,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1" s="88">
+    <row r="67" ht="15.75" customHeight="1" s="91">
       <c r="A67" s="36" t="inlineStr">
         <is>
           <t>간식은 입력 가능</t>
@@ -8058,7 +8150,7 @@
       </c>
       <c r="C67" s="41" t="n"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1" s="88">
+    <row r="68" ht="15.75" customHeight="1" s="91">
       <c r="A68" s="68" t="inlineStr">
         <is>
           <t>운영원 표시</t>
@@ -8075,7 +8167,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="15.75" customHeight="1" s="88">
+    <row r="69" ht="15.75" customHeight="1" s="91">
       <c r="A69" s="36" t="inlineStr">
         <is>
           <t>도시락/대체식</t>
@@ -8092,12 +8184,12 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1" s="88">
+    <row r="70" ht="15.75" customHeight="1" s="91">
       <c r="A70" s="70" t="n"/>
       <c r="B70" s="70" t="n"/>
       <c r="C70" s="70" t="n"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1" s="88">
+    <row r="71" ht="15.75" customHeight="1" s="91">
       <c r="A71" s="72" t="inlineStr">
         <is>
           <t>📌 5주차 없는 달</t>
@@ -8114,12 +8206,12 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1" s="88">
+    <row r="72" ht="15.75" customHeight="1" s="91">
       <c r="A72" s="70" t="n"/>
       <c r="B72" s="70" t="n"/>
       <c r="C72" s="70" t="n"/>
     </row>
-    <row r="73" ht="22.5" customHeight="1" s="88">
+    <row r="73" ht="22.5" customHeight="1" s="91">
       <c r="A73" s="69" t="inlineStr">
         <is>
           <t>📌 원명 코드 (대괄호 입력 시 정확히 입력)</t>
@@ -8128,7 +8220,7 @@
       <c r="B73" s="69" t="n"/>
       <c r="C73" s="69" t="n"/>
     </row>
-    <row r="74" ht="19.5" customHeight="1" s="88">
+    <row r="74" ht="19.5" customHeight="1" s="91">
       <c r="A74" s="70" t="inlineStr">
         <is>
           <t>ECC 6개원</t>
@@ -8141,7 +8233,7 @@
       </c>
       <c r="C74" s="70" t="n"/>
     </row>
-    <row r="75" ht="19.5" customHeight="1" s="88">
+    <row r="75" ht="19.5" customHeight="1" s="91">
       <c r="A75" s="41" t="inlineStr">
         <is>
           <t>POLY (1)</t>
@@ -8154,7 +8246,7 @@
       </c>
       <c r="C75" s="41" t="n"/>
     </row>
-    <row r="76" ht="19.5" customHeight="1" s="88">
+    <row r="76" ht="19.5" customHeight="1" s="91">
       <c r="A76" s="70" t="inlineStr">
         <is>
           <t>POLY (2)</t>
@@ -8167,7 +8259,7 @@
       </c>
       <c r="C76" s="70" t="n"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1" s="88">
+    <row r="77" ht="15.75" customHeight="1" s="91">
       <c r="A77" s="41" t="inlineStr">
         <is>
           <t>POLY (3)</t>
@@ -8180,7 +8272,7 @@
       </c>
       <c r="C77" s="41" t="n"/>
     </row>
-    <row r="78" ht="19.5" customHeight="1" s="88">
+    <row r="78" ht="19.5" customHeight="1" s="91">
       <c r="A78" s="68" t="inlineStr">
         <is>
           <t>라이즈 7개원</t>
@@ -8193,7 +8285,7 @@
       </c>
       <c r="C78" s="70" t="n"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1" s="88">
+    <row r="79" ht="15.75" customHeight="1" s="91">
       <c r="A79" s="41" t="inlineStr">
         <is>
           <t>MB / SLP</t>
@@ -8206,7 +8298,7 @@
       </c>
       <c r="C79" s="41" t="n"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1" s="88">
+    <row r="80" ht="15.75" customHeight="1" s="91">
       <c r="A80" s="68" t="inlineStr">
         <is>
           <t>알티오라</t>
@@ -8219,7 +8311,7 @@
       </c>
       <c r="C80" s="70" t="n"/>
     </row>
-    <row r="81" ht="19.5" customHeight="1" s="88">
+    <row r="81" ht="19.5" customHeight="1" s="91">
       <c r="A81" s="36" t="inlineStr">
         <is>
           <t>기타</t>
@@ -8232,7 +8324,7 @@
       </c>
       <c r="C81" s="41" t="n"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1" s="88">
+    <row r="82" ht="15.75" customHeight="1" s="91">
       <c r="A82" s="68" t="inlineStr">
         <is>
           <t>찰리스</t>
@@ -8245,12 +8337,12 @@
       </c>
       <c r="C82" s="70" t="n"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1" s="88">
+    <row r="83" ht="15.75" customHeight="1" s="91">
       <c r="A83" s="41" t="n"/>
       <c r="B83" s="41" t="n"/>
       <c r="C83" s="41" t="n"/>
     </row>
-    <row r="84" ht="23.25" customHeight="1" s="88">
+    <row r="84" ht="23.25" customHeight="1" s="91">
       <c r="A84" s="69" t="inlineStr">
         <is>
           <t>📌 브랜드 코드 (전체 적용 시)</t>
@@ -8259,7 +8351,7 @@
       <c r="B84" s="69" t="n"/>
       <c r="C84" s="69" t="n"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1" s="88">
+    <row r="85" ht="15.75" customHeight="1" s="91">
       <c r="A85" s="41" t="inlineStr">
         <is>
           <t>P</t>
@@ -8276,7 +8368,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="15.75" customHeight="1" s="88">
+    <row r="86" ht="15.75" customHeight="1" s="91">
       <c r="A86" s="70" t="inlineStr">
         <is>
           <t>E</t>
@@ -8293,7 +8385,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="15.75" customHeight="1" s="88">
+    <row r="87" ht="15.75" customHeight="1" s="91">
       <c r="A87" s="41" t="inlineStr">
         <is>
           <t>R</t>
@@ -8310,7 +8402,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="15.75" customHeight="1" s="88">
+    <row r="88" ht="15.75" customHeight="1" s="91">
       <c r="A88" s="70" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -8327,7 +8419,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="15.75" customHeight="1" s="88">
+    <row r="89" ht="15.75" customHeight="1" s="91">
       <c r="A89" s="41" t="inlineStr">
         <is>
           <t>MB</t>
@@ -8344,12 +8436,12 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="15.75" customHeight="1" s="88">
+    <row r="90" ht="15.75" customHeight="1" s="91">
       <c r="A90" s="70" t="n"/>
       <c r="B90" s="70" t="n"/>
       <c r="C90" s="70" t="n"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1" s="88">
+    <row r="91" ht="15.75" customHeight="1" s="91">
       <c r="A91" s="69" t="inlineStr">
         <is>
           <t>📌 주의사항</t>
@@ -8358,7 +8450,7 @@
       <c r="B91" s="69" t="n"/>
       <c r="C91" s="69" t="n"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1" s="88">
+    <row r="92" ht="15.75" customHeight="1" s="91">
       <c r="A92" s="68" t="inlineStr">
         <is>
           <t>동탄POLY 오전간식</t>
@@ -8375,7 +8467,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="15.75" customHeight="1" s="88">
+    <row r="93" ht="15.75" customHeight="1" s="91">
       <c r="A93" s="36" t="inlineStr">
         <is>
           <t>생일간식</t>
@@ -8392,7 +8484,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="15.75" customHeight="1" s="88">
+    <row r="94" ht="15.75" customHeight="1" s="91">
       <c r="A94" s="68" t="inlineStr">
         <is>
           <t>돌봄간식</t>
@@ -8405,7 +8497,7 @@
       </c>
       <c r="C94" s="70" t="n"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1" s="88">
+    <row r="95" ht="15.75" customHeight="1" s="91">
       <c r="A95" s="36" t="inlineStr">
         <is>
           <t>후식과일</t>
@@ -8422,7 +8514,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="15.75" customHeight="1" s="88">
+    <row r="96" ht="15.75" customHeight="1" s="91">
       <c r="A96" s="68" t="inlineStr">
         <is>
           <t>반찬5</t>
@@ -8439,7 +8531,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="15.75" customHeight="1" s="88">
+    <row r="97" ht="15.75" customHeight="1" s="91">
       <c r="A97" s="36" t="inlineStr">
         <is>
           <t>원명 오타</t>
@@ -8456,7 +8548,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="15.75" customHeight="1" s="88">
+    <row r="99" ht="15.75" customHeight="1" s="91">
       <c r="A99" s="73" t="inlineStr">
         <is>
           <t>📌 원별 참조표 — 새 원 추가 방법</t>
@@ -8465,7 +8557,7 @@
       <c r="B99" s="72" t="n"/>
       <c r="C99" s="72" t="n"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1" s="88">
+    <row r="100" ht="15.75" customHeight="1" s="91">
       <c r="A100" s="74" t="inlineStr">
         <is>
           <t>새 원 추가 시</t>
@@ -8482,7 +8574,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="15.75" customHeight="1" s="88">
+    <row r="101" ht="15.75" customHeight="1" s="91">
       <c r="A101" s="75" t="inlineStr">
         <is>
           <t>슬라이드수</t>
@@ -8499,7 +8591,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="15.75" customHeight="1" s="88">
+    <row r="102" ht="15.75" customHeight="1" s="91">
       <c r="A102" s="74" t="inlineStr">
         <is>
           <t>간식라벨</t>
@@ -8516,7 +8608,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="15.75" customHeight="1" s="88">
+    <row r="103" ht="15.75" customHeight="1" s="91">
       <c r="A103" s="75" t="inlineStr">
         <is>
           <t>돌봄간식</t>
@@ -8533,7 +8625,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="15.75" customHeight="1" s="88">
+    <row r="104" ht="15.75" customHeight="1" s="91">
       <c r="A104" s="74" t="inlineStr">
         <is>
           <t>생일간식</t>
@@ -8550,7 +8642,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="15.75" customHeight="1" s="88">
+    <row r="105" ht="15.75" customHeight="1" s="91">
       <c r="A105" s="75" t="inlineStr">
         <is>
           <t>후식과일</t>
@@ -8567,7 +8659,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="15.75" customHeight="1" s="88">
+    <row r="106" ht="15.75" customHeight="1" s="91">
       <c r="A106" s="74" t="inlineStr">
         <is>
           <t>알러지표기</t>
@@ -8584,12 +8676,12 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="15.75" customHeight="1" s="88">
+    <row r="107" ht="15.75" customHeight="1" s="91">
       <c r="A107" s="75" t="n"/>
       <c r="B107" s="75" t="n"/>
       <c r="C107" s="75" t="n"/>
     </row>
-    <row r="108" ht="28.5" customHeight="1" s="88">
+    <row r="108" ht="28.5" customHeight="1" s="91">
       <c r="A108" s="73" t="inlineStr">
         <is>
           <t>📌 타입 자동 판단 규칙 (참고용)</t>
@@ -8598,7 +8690,7 @@
       <c r="B108" s="72" t="n"/>
       <c r="C108" s="72" t="n"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1" s="88">
+    <row r="109" ht="15.75" customHeight="1" s="91">
       <c r="A109" s="75" t="inlineStr">
         <is>
           <t>타입A</t>
@@ -8615,7 +8707,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="15.75" customHeight="1" s="88">
+    <row r="110" ht="15.75" customHeight="1" s="91">
       <c r="A110" s="74" t="inlineStr">
         <is>
           <t>타입C</t>
@@ -8632,7 +8724,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="15.75" customHeight="1" s="88">
+    <row r="111" ht="15.75" customHeight="1" s="91">
       <c r="A111" s="75" t="inlineStr">
         <is>
           <t>타입B</t>
@@ -8649,7 +8741,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="15.75" customHeight="1" s="88">
+    <row r="112" ht="15.75" customHeight="1" s="91">
       <c r="A112" s="74" t="inlineStr">
         <is>
           <t>타입D</t>
@@ -8666,7 +8758,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="15.75" customHeight="1" s="88">
+    <row r="113" ht="15.75" customHeight="1" s="91">
       <c r="A113" s="75" t="inlineStr">
         <is>
           <t>타입E</t>
@@ -8683,7 +8775,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="15.75" customHeight="1" s="88">
+    <row r="114" ht="15.75" customHeight="1" s="91">
       <c r="A114" s="74" t="inlineStr">
         <is>
           <t>타입F</t>
@@ -8700,7 +8792,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="15.75" customHeight="1" s="88">
+    <row r="115" ht="15.75" customHeight="1" s="91">
       <c r="A115" s="75" t="inlineStr">
         <is>
           <t>타입G</t>
@@ -8717,7 +8809,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="15.75" customHeight="1" s="88">
+    <row r="116" ht="15.75" customHeight="1" s="91">
       <c r="A116" s="74" t="inlineStr">
         <is>
           <t>타입송파E</t>
